--- a/12601472 (1).xlsx
+++ b/12601472 (1).xlsx
@@ -5,23 +5,24 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAM\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAM\Projects-Code\University-Codes\PYTHON\CA_MINI_PROJECT_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1872491C-CE8B-42BB-8A5C-8D2A8191E27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B6A07CA-C694-4AE5-A5BF-9E3C5E5B5E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +329,15 @@
   <si>
     <t>Enjoye the day without doing anything</t>
   </si>
+  <si>
+    <t>Boring day, too much break bewteen classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">was not feeling well </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day went as usual, little bit borring </t>
+  </si>
 </sst>
 </file>
 
@@ -336,7 +346,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -419,8 +429,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +452,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -641,7 +662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -680,12 +701,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -696,6 +711,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1214,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N412"/>
+  <dimension ref="A1:N415"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -1229,70 +1277,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="19"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="29">
         <v>12601472</v>
       </c>
-      <c r="G2" s="19"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="19"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
     </row>
     <row r="5" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1364,11 +1412,11 @@
         <v>50</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I5:I80" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I83" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>970</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J80" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J83" si="1">IF(I6="","",1440-I6)</f>
         <v>470</v>
       </c>
       <c r="K6" s="16" t="s">
@@ -1385,28 +1433,28 @@
       </c>
     </row>
     <row r="7" spans="1:14" s="13" customFormat="1" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="24">
+      <c r="A7" s="18">
         <v>46248</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="19">
         <v>330</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="19">
         <v>60</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="19">
         <v>60</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="19">
         <v>350</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="19">
         <v>6</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="19">
         <v>60</v>
       </c>
       <c r="I7" s="10">
@@ -1417,42 +1465,42 @@
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="L7" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="N7" s="27" t="s">
+      <c r="N7" s="21" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="13" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="24">
+      <c r="A8" s="18">
         <v>46249</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="19">
         <v>420</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="19">
         <v>60</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="19">
         <v>60</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="19">
         <v>60</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="19">
         <v>0</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="19">
         <v>200</v>
       </c>
       <c r="I8" s="10">
@@ -1463,42 +1511,42 @@
         <f t="shared" si="1"/>
         <v>640</v>
       </c>
-      <c r="K8" s="26" t="s">
+      <c r="K8" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="26" t="s">
+      <c r="L8" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="M8" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="N8" s="27" t="s">
+      <c r="N8" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="13" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="24">
+      <c r="A9" s="18">
         <v>46250</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="19">
         <v>420</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="19">
         <v>60</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="19">
         <v>50</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="19">
         <v>40</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="19">
         <v>0</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="19">
         <v>200</v>
       </c>
       <c r="I9" s="10">
@@ -1509,42 +1557,42 @@
         <f t="shared" si="1"/>
         <v>670</v>
       </c>
-      <c r="K9" s="26" t="s">
+      <c r="K9" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="26" t="s">
+      <c r="L9" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="M9" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="27" t="s">
+      <c r="N9" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="13" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="24">
+      <c r="A10" s="18">
         <v>46251</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="19">
         <v>330</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="19">
         <v>50</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="19">
         <v>120</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="19">
         <v>300</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="19">
         <v>6</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="19">
         <v>120</v>
       </c>
       <c r="I10" s="10">
@@ -1555,42 +1603,42 @@
         <f t="shared" si="1"/>
         <v>520</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="L10" s="26" t="s">
+      <c r="L10" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="N10" s="27" t="s">
+      <c r="N10" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="13" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="24">
+      <c r="A11" s="18">
         <v>46252</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="19">
         <v>400</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="19">
         <v>30</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="19">
         <v>60</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="19">
         <v>120</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="19">
         <v>400</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="19">
         <v>5</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="19">
         <v>60</v>
       </c>
       <c r="I11" s="10">
@@ -1601,42 +1649,42 @@
         <f t="shared" si="1"/>
         <v>370</v>
       </c>
-      <c r="K11" s="26" t="s">
+      <c r="K11" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="26" t="s">
+      <c r="L11" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="N11" s="27" t="s">
+      <c r="N11" s="21" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="13" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="24">
+      <c r="A12" s="18">
         <v>46253</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="19">
         <v>400</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="19">
         <v>30</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="19">
         <v>60</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="19">
         <v>60</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="19">
         <v>400</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="19">
         <v>5</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="19">
         <v>80</v>
       </c>
       <c r="I12" s="10">
@@ -1647,42 +1695,42 @@
         <f t="shared" si="1"/>
         <v>410</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="L12" s="26" t="s">
+      <c r="L12" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="M12" s="26" t="s">
+      <c r="M12" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="N12" s="27" t="s">
+      <c r="N12" s="21" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="13" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="24">
+      <c r="A13" s="18">
         <v>46254</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="19">
         <v>400</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="19">
         <v>30</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="19">
         <v>60</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="19">
         <v>120</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="19">
         <v>400</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="19">
         <v>6</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="19">
         <v>60</v>
       </c>
       <c r="I13" s="10">
@@ -1693,42 +1741,42 @@
         <f t="shared" si="1"/>
         <v>370</v>
       </c>
-      <c r="K13" s="26" t="s">
+      <c r="K13" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="L13" s="26" t="s">
+      <c r="L13" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="M13" s="26" t="s">
+      <c r="M13" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="N13" s="27" t="s">
+      <c r="N13" s="21" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="13" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="24">
+      <c r="A14" s="18">
         <v>46255</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="19">
         <v>400</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="19">
         <v>30</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="19">
         <v>60</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="19">
         <v>120</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="19">
         <v>400</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="19">
         <v>6</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="19">
         <v>60</v>
       </c>
       <c r="I14" s="10">
@@ -1739,42 +1787,42 @@
         <f t="shared" si="1"/>
         <v>370</v>
       </c>
-      <c r="K14" s="26" t="s">
+      <c r="K14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="L14" s="26" t="s">
+      <c r="L14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="M14" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="N14" s="27" t="s">
+      <c r="N14" s="21" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="24">
+      <c r="A15" s="18">
         <v>46256</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="19">
         <v>400</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="19">
         <v>30</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="19">
         <v>60</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="19">
         <v>200</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="19">
         <v>0</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="19">
         <v>200</v>
       </c>
       <c r="I15" s="10">
@@ -1785,42 +1833,42 @@
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K15" s="26" t="s">
+      <c r="K15" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="L15" s="26" t="s">
+      <c r="L15" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="N15" s="27" t="s">
+      <c r="N15" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="13" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="24">
+      <c r="A16" s="18">
         <v>46257</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="19">
         <v>400</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="19">
         <v>0</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="19">
         <v>0</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="19">
         <v>0</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="19">
         <v>300</v>
       </c>
       <c r="I16" s="10">
@@ -1831,16 +1879,16 @@
         <f t="shared" si="1"/>
         <v>740</v>
       </c>
-      <c r="K16" s="26" t="s">
+      <c r="K16" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="L16" s="26" t="s">
+      <c r="L16" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="26" t="s">
+      <c r="M16" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="N16" s="27" t="s">
+      <c r="N16" s="21" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2535,530 +2583,602 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8">
+      <c r="A32" s="22">
+        <v>46274</v>
+      </c>
+      <c r="B32" s="23">
+        <v>350</v>
+      </c>
+      <c r="C32" s="23">
+        <v>30</v>
+      </c>
+      <c r="D32" s="23">
+        <v>60</v>
+      </c>
+      <c r="E32" s="23">
+        <v>0</v>
+      </c>
+      <c r="F32" s="23">
+        <v>400</v>
+      </c>
+      <c r="G32" s="23">
+        <v>5</v>
+      </c>
+      <c r="H32" s="23">
+        <v>80</v>
+      </c>
+      <c r="I32" s="24">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J32" s="24">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+      <c r="K32" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L32" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="M32" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" s="26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
         <v>46273</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B33" s="9">
         <v>330</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C33" s="9">
         <v>30</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D33" s="9">
         <v>60</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E33" s="9">
         <v>40</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F33" s="9">
         <v>400</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G33" s="9">
         <v>5</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H33" s="9">
         <v>30</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="K33" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L33" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M32" s="11" t="s">
+      <c r="M33" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N32" s="12" t="s">
+      <c r="N33" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+    <row r="34" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B34" s="9">
         <v>360</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C34" s="9">
         <v>30</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D34" s="9">
         <v>70</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E34" s="9">
         <v>46</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F34" s="9">
         <v>0</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G34" s="9">
         <v>0</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H34" s="9">
         <v>60</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
         <v>566</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
         <v>874</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="K34" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L34" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M33" s="11" t="s">
+      <c r="M34" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N33" s="12" t="s">
+      <c r="N34" s="12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="8">
+    <row r="35" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
         <v>46276</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B35" s="9">
         <v>360</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C35" s="9">
         <v>30</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D35" s="9">
         <v>40</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E35" s="9">
         <v>40</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F35" s="9">
         <v>350</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G35" s="9">
         <v>6</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H35" s="9">
         <v>60</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M34" s="11" t="s">
+      <c r="M35" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N34" s="12" t="s">
+      <c r="N35" s="12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8">
+    <row r="36" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
         <v>46277</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B36" s="9">
         <v>360</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C36" s="9">
         <v>30</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D36" s="9">
         <v>150</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E36" s="9">
         <v>0</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F36" s="9">
         <v>0</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G36" s="9">
         <v>0</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H36" s="9">
         <v>400</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
         <v>940</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L36" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M35" s="11" t="s">
+      <c r="M36" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N35" s="12" t="s">
+      <c r="N36" s="12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+    <row r="37" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B37" s="9">
         <v>420</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C37" s="9">
         <v>0</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D37" s="9">
         <v>120</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E37" s="9">
         <v>90</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F37" s="9">
         <v>0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G37" s="9">
         <v>0</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H37" s="9">
         <v>119</v>
       </c>
-      <c r="I36" s="10">
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
         <v>749</v>
       </c>
-      <c r="J36" s="10">
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
         <v>691</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="K37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M36" s="11" t="s">
+      <c r="M37" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N36" s="12" t="s">
+      <c r="N37" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+    <row r="38" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="33">
+        <v>46279</v>
+      </c>
+      <c r="B38" s="34">
+        <v>360</v>
+      </c>
+      <c r="C38" s="34">
+        <v>30</v>
+      </c>
+      <c r="D38" s="34">
+        <v>60</v>
+      </c>
+      <c r="E38" s="34">
+        <v>120</v>
+      </c>
+      <c r="F38" s="34">
+        <v>400</v>
+      </c>
+      <c r="G38" s="34">
+        <v>5</v>
+      </c>
+      <c r="H38" s="34">
+        <v>60</v>
+      </c>
+      <c r="I38" s="10">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="J38" s="10">
+        <f t="shared" si="1"/>
+        <v>410</v>
+      </c>
+      <c r="K38" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="L38" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="M38" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="N38" s="36" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="33">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="34">
+        <v>360</v>
+      </c>
+      <c r="C39" s="34">
+        <v>30</v>
+      </c>
+      <c r="D39" s="34">
+        <v>60</v>
+      </c>
+      <c r="E39" s="34">
+        <v>70</v>
+      </c>
+      <c r="F39" s="34">
+        <v>400</v>
+      </c>
+      <c r="G39" s="34">
+        <v>6</v>
+      </c>
+      <c r="H39" s="34">
+        <v>60</v>
+      </c>
+      <c r="I39" s="10">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J39" s="10">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="K39" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="L39" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="M39" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="N39" s="36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B40" s="9">
         <v>360</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C40" s="9">
         <v>35</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D40" s="9">
         <v>120</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E40" s="9">
         <v>0</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F40" s="9">
         <v>400</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G40" s="9">
         <v>8</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H40" s="9">
         <v>119</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
         <v>1034</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
         <v>406</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="K40" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L40" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M37" s="11" t="s">
+      <c r="M40" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N37" s="12" t="s">
+      <c r="N40" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+    <row r="41" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B41" s="9">
         <v>420</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C41" s="9">
         <v>35</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D41" s="9">
         <v>120</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E41" s="9">
         <v>43</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F41" s="9">
         <v>400</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G41" s="9">
         <v>3</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H41" s="9">
         <v>119</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
         <v>1137</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
         <v>303</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K41" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L41" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M38" s="11" t="s">
+      <c r="M41" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N38" s="12" t="s">
+      <c r="N41" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+    <row r="42" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B42" s="9">
         <v>420</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C42" s="9">
         <v>35</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D42" s="9">
         <v>120</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E42" s="9">
         <v>0</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F42" s="9">
         <v>400</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G42" s="9">
         <v>3</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H42" s="9">
         <v>119</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I42" s="10">
         <f t="shared" si="0"/>
         <v>1094</v>
       </c>
-      <c r="J39" s="10">
+      <c r="J42" s="10">
         <f t="shared" si="1"/>
         <v>346</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="K42" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="L42" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="M39" s="11" t="s">
+      <c r="M42" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N39" s="12" t="s">
+      <c r="N42" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+    <row r="43" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B43" s="9">
         <v>420</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C43" s="9">
         <v>35</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D43" s="9">
         <v>81</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E43" s="9">
         <v>41</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F43" s="9">
         <v>285</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G43" s="9">
         <v>2</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H43" s="9">
         <v>119</v>
       </c>
-      <c r="I40" s="10">
+      <c r="I43" s="10">
         <f t="shared" si="0"/>
         <v>981</v>
       </c>
-      <c r="J40" s="10">
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
         <v>459</v>
       </c>
-      <c r="K40" s="11" t="s">
+      <c r="K43" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L43" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="M40" s="11" t="s">
+      <c r="M43" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N40" s="12" t="s">
+      <c r="N43" s="12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+    <row r="44" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B44" s="9">
         <v>420</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C44" s="9">
         <v>35</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D44" s="9">
         <v>0</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E44" s="9">
         <v>0</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F44" s="9">
         <v>0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G44" s="9">
         <v>0</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H44" s="9">
         <v>360</v>
       </c>
-      <c r="I41" s="10">
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
         <v>815</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
         <v>625</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="K44" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L44" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M41" s="11" t="s">
+      <c r="M44" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N41" s="12" t="s">
+      <c r="N44" s="12" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
-    </row>
-    <row r="43" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
-    </row>
-    <row r="44" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8"/>
@@ -3862,11 +3982,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" ref="I81:I144" si="2">IF(SUM(B81:F81,H81)=0,"",SUM(B81:F81,H81))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" ref="J81:J144" si="3">IF(I81="","",1440-I81)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3884,11 +4004,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3906,11 +4026,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3928,11 +4048,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I84:I147" si="2">IF(SUM(B84:F84,H84)=0,"",SUM(B84:F84,H84))</f>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J84:J147" si="3">IF(I84="","",1440-I84)</f>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -5270,11 +5390,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" ref="I145:I208" si="4">IF(SUM(B145:F145,H145)=0,"",SUM(B145:F145,H145))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" ref="J145:J208" si="5">IF(I145="","",1440-I145)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -5292,11 +5412,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5314,11 +5434,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5336,11 +5456,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I148:I211" si="4">IF(SUM(B148:F148,H148)=0,"",SUM(B148:F148,H148))</f>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J148:J211" si="5">IF(I148="","",1440-I148)</f>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -6678,11 +6798,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" ref="I209:I272" si="6">IF(SUM(B209:F209,H209)=0,"",SUM(B209:F209,H209))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" ref="J209:J272" si="7">IF(I209="","",1440-I209)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6700,11 +6820,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6722,11 +6842,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6744,11 +6864,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I212:I275" si="6">IF(SUM(B212:F212,H212)=0,"",SUM(B212:F212,H212))</f>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J212:J275" si="7">IF(I212="","",1440-I212)</f>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -8086,11 +8206,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" ref="I273:I336" si="8">IF(SUM(B273:F273,H273)=0,"",SUM(B273:F273,H273))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" ref="J273:J336" si="9">IF(I273="","",1440-I273)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -8108,11 +8228,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -8130,11 +8250,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -8152,11 +8272,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I276:I339" si="8">IF(SUM(B276:F276,H276)=0,"",SUM(B276:F276,H276))</f>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J276:J339" si="9">IF(I276="","",1440-I276)</f>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -9494,11 +9614,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" ref="I337:I400" si="10">IF(SUM(B337:F337,H337)=0,"",SUM(B337:F337,H337))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" ref="J337:J400" si="11">IF(I337="","",1440-I337)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9516,11 +9636,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9538,11 +9658,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9560,11 +9680,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I340:I403" si="10">IF(SUM(B340:F340,H340)=0,"",SUM(B340:F340,H340))</f>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J340:J403" si="11">IF(I340="","",1440-I340)</f>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -10902,11 +11022,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" ref="I401:I464" si="12">IF(SUM(B401:F401,H401)=0,"",SUM(B401:F401,H401))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" ref="J401:J464" si="13">IF(I401="","",1440-I401)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K401" s="11"/>
@@ -10924,11 +11044,11 @@
       <c r="G402" s="9"/>
       <c r="H402" s="9"/>
       <c r="I402" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J402" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K402" s="11"/>
@@ -10946,11 +11066,11 @@
       <c r="G403" s="9"/>
       <c r="H403" s="9"/>
       <c r="I403" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J403" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K403" s="11"/>
@@ -10968,11 +11088,11 @@
       <c r="G404" s="9"/>
       <c r="H404" s="9"/>
       <c r="I404" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I404:I415" si="12">IF(SUM(B404:F404,H404)=0,"",SUM(B404:F404,H404))</f>
         <v/>
       </c>
       <c r="J404" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J404:J415" si="13">IF(I404="","",1440-I404)</f>
         <v/>
       </c>
       <c r="K404" s="11"/>
@@ -11002,7 +11122,7 @@
       <c r="M405" s="11"/>
       <c r="N405" s="12"/>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="8"/>
       <c r="B406" s="9"/>
       <c r="C406" s="9"/>
@@ -11024,7 +11144,7 @@
       <c r="M406" s="11"/>
       <c r="N406" s="12"/>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="8"/>
       <c r="B407" s="9"/>
       <c r="C407" s="9"/>
@@ -11046,7 +11166,7 @@
       <c r="M407" s="11"/>
       <c r="N407" s="12"/>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="8"/>
       <c r="B408" s="9"/>
       <c r="C408" s="9"/>
@@ -11156,6 +11276,72 @@
       <c r="M412" s="11"/>
       <c r="N412" s="12"/>
     </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A413" s="8"/>
+      <c r="B413" s="9"/>
+      <c r="C413" s="9"/>
+      <c r="D413" s="9"/>
+      <c r="E413" s="9"/>
+      <c r="F413" s="9"/>
+      <c r="G413" s="9"/>
+      <c r="H413" s="9"/>
+      <c r="I413" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J413" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K413" s="11"/>
+      <c r="L413" s="11"/>
+      <c r="M413" s="11"/>
+      <c r="N413" s="12"/>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A414" s="8"/>
+      <c r="B414" s="9"/>
+      <c r="C414" s="9"/>
+      <c r="D414" s="9"/>
+      <c r="E414" s="9"/>
+      <c r="F414" s="9"/>
+      <c r="G414" s="9"/>
+      <c r="H414" s="9"/>
+      <c r="I414" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J414" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K414" s="11"/>
+      <c r="L414" s="11"/>
+      <c r="M414" s="11"/>
+      <c r="N414" s="12"/>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A415" s="8"/>
+      <c r="B415" s="9"/>
+      <c r="C415" s="9"/>
+      <c r="D415" s="9"/>
+      <c r="E415" s="9"/>
+      <c r="F415" s="9"/>
+      <c r="G415" s="9"/>
+      <c r="H415" s="9"/>
+      <c r="I415" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J415" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K415" s="11"/>
+      <c r="L415" s="11"/>
+      <c r="M415" s="11"/>
+      <c r="N415" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:N1"/>
@@ -11165,19 +11351,20 @@
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J412">
+  <phoneticPr fontId="13" type="noConversion"/>
+  <conditionalFormatting sqref="J6:J415">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" prompt="Select today's overall feeling" sqref="K6:K412" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's overall feeling" sqref="K6:K37 K40:K415" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L412" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L37 L40:L415" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M412" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M37 M40:M415" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
